--- a/practice/answers/q031.xlsx
+++ b/practice/answers/q031.xlsx
@@ -70116,7 +70116,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>(d) SY Manness cleared 60 bu/ac more often (73% of its 2023 results against Brandon's 55%). The fractions say how dependably each variety reaches a target the averages only hint at -- but the totals matter too: Manness's 73% rests on just 11 results against Brandon's 84, so it is the less firmly established figure.</t>

--- a/practice/answers/q031.xlsx
+++ b/practice/answers/q031.xlsx
@@ -17,9 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -51,12 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,19 +70,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -70081,7 +70081,7 @@
         <f>COUNTIFS(Data!$C$2:$C$2399,"AAC BRANDON (BW 932)",Data!$A$2:$A$2399,2023,Data!$F$2:$F$2399,"&gt;60")</f>
         <v/>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <f>COUNTIFS(Data!$C$2:$C$2399,"SY MANNESS",Data!$A$2:$A$2399,2023,Data!$F$2:$F$2399,"&gt;60")</f>
         <v/>
       </c>
@@ -70092,7 +70092,7 @@
           <t>All 2023 rows (b/c)</t>
         </is>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <f>COUNTIFS(Data!$C$2:$C$2399,"AAC BRANDON (BW 932)",Data!$A$2:$A$2399,2023)</f>
         <v/>
       </c>
@@ -70107,17 +70107,17 @@
           <t>Fraction above 60 (b/c)</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <f>B2/B3</f>
         <v/>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <f>C2/C3</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>(d) SY Manness cleared 60 bu/ac more often (73% of its 2023 results against Brandon's 55%). The fractions say how dependably each variety reaches a target the averages only hint at -- but the totals matter too: Manness's 73% rests on just 11 results against Brandon's 84, so it is the less firmly established figure.</t>
         </is>
@@ -70131,28 +70131,28 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Part (a)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Part (b)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Part (c)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Part (d)</t>
         </is>
